--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_HAPOEL IBI TEL AVIV.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>77.6262</v>
+        <v>63.0531</v>
       </c>
       <c r="E2" t="n">
-        <v>83.6776</v>
+        <v>41.6414</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.0519</v>
+        <v>21.4117</v>
       </c>
       <c r="G2" t="n">
-        <v>55.6749</v>
+        <v>49.9</v>
       </c>
       <c r="H2" t="n">
-        <v>53.6629</v>
+        <v>36.5014</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0119</v>
+        <v>13.3986</v>
       </c>
       <c r="J2" t="n">
-        <v>88.1681</v>
+        <v>83.27379999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>72.09779999999999</v>
+        <v>57.9424</v>
       </c>
       <c r="L2" t="n">
-        <v>16.0698</v>
+        <v>25.3316</v>
       </c>
       <c r="M2" t="n">
-        <v>-32.4934</v>
+        <v>-33.3737</v>
       </c>
       <c r="N2" t="n">
-        <v>-18.4347</v>
+        <v>-21.4408</v>
       </c>
       <c r="O2" t="n">
-        <v>-14.0585</v>
+        <v>-11.9332</v>
       </c>
       <c r="P2" t="n">
-        <v>-6.7264</v>
+        <v>-21.5715</v>
       </c>
       <c r="Q2" t="n">
-        <v>-69.81789999999999</v>
+        <v>-94.1724</v>
       </c>
       <c r="R2" t="n">
-        <v>63.0916</v>
+        <v>72.6011</v>
       </c>
       <c r="S2" t="n">
-        <v>47.0641</v>
+        <v>1.565900000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>41.4591</v>
+        <v>-4.6636</v>
       </c>
       <c r="U2" t="n">
-        <v>5.605</v>
+        <v>6.2293</v>
       </c>
       <c r="V2" t="n">
-        <v>-18.3866</v>
+        <v>33.1586</v>
       </c>
       <c r="W2" t="n">
-        <v>23.8682</v>
+        <v>57.2035</v>
       </c>
       <c r="X2" t="n">
-        <v>-42.2547</v>
+        <v>-24.0449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>60.4285</v>
+        <v>44.782</v>
       </c>
       <c r="E3" t="n">
-        <v>35.7326</v>
+        <v>50.7923</v>
       </c>
       <c r="F3" t="n">
-        <v>24.696</v>
+        <v>-6.0106</v>
       </c>
       <c r="G3" t="n">
-        <v>49.9</v>
+        <v>55.6749</v>
       </c>
       <c r="H3" t="n">
-        <v>36.5014</v>
+        <v>53.6629</v>
       </c>
       <c r="I3" t="n">
-        <v>13.3986</v>
+        <v>2.0119</v>
       </c>
       <c r="J3" t="n">
-        <v>83.27379999999999</v>
+        <v>88.1681</v>
       </c>
       <c r="K3" t="n">
-        <v>57.9424</v>
+        <v>72.09779999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>25.3316</v>
+        <v>16.0698</v>
       </c>
       <c r="M3" t="n">
-        <v>-33.3737</v>
+        <v>-32.4934</v>
       </c>
       <c r="N3" t="n">
-        <v>-21.4408</v>
+        <v>-18.4347</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.9332</v>
+        <v>-14.0585</v>
       </c>
       <c r="P3" t="n">
-        <v>-21.5715</v>
+        <v>-6.7264</v>
       </c>
       <c r="Q3" t="n">
-        <v>-94.1724</v>
+        <v>-69.81789999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>72.6011</v>
+        <v>63.0916</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0583</v>
+        <v>14.2204</v>
       </c>
       <c r="T3" t="n">
-        <v>-10.5724</v>
+        <v>8.573399999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>9.5137</v>
+        <v>5.6464</v>
       </c>
       <c r="V3" t="n">
-        <v>33.1586</v>
+        <v>-18.3866</v>
       </c>
       <c r="W3" t="n">
-        <v>57.2035</v>
+        <v>23.8682</v>
       </c>
       <c r="X3" t="n">
-        <v>-24.0449</v>
+        <v>-42.2547</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>27.506</v>
+        <v>40.7147</v>
       </c>
       <c r="E4" t="n">
-        <v>26.0974</v>
+        <v>32.3522</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4087</v>
+        <v>8.362500000000001</v>
       </c>
       <c r="G4" t="n">
         <v>24.4114</v>
@@ -766,13 +766,13 @@
         <v>56.3646</v>
       </c>
       <c r="S4" t="n">
-        <v>-24.0269</v>
+        <v>-10.8184</v>
       </c>
       <c r="T4" t="n">
-        <v>-16.2395</v>
+        <v>-9.9842</v>
       </c>
       <c r="U4" t="n">
-        <v>-7.787599999999999</v>
+        <v>-0.8341000000000002</v>
       </c>
       <c r="V4" t="n">
         <v>17.6117</v>
@@ -799,13 +799,13 @@
         <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>15.7767</v>
+        <v>34.2703</v>
       </c>
       <c r="E5" t="n">
-        <v>8.4236</v>
+        <v>20.8242</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3527</v>
+        <v>13.4457</v>
       </c>
       <c r="G5" t="n">
         <v>55.9386</v>
@@ -844,13 +844,13 @@
         <v>48.0149</v>
       </c>
       <c r="S5" t="n">
-        <v>-24.0135</v>
+        <v>-5.5195</v>
       </c>
       <c r="T5" t="n">
-        <v>-22.3545</v>
+        <v>-9.9541</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.6591</v>
+        <v>4.4343</v>
       </c>
       <c r="V5" t="n">
         <v>6.1185</v>
@@ -877,13 +877,13 @@
         <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>14.7013</v>
+        <v>20.3561</v>
       </c>
       <c r="E6" t="n">
-        <v>14.265</v>
+        <v>16.5487</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4363000000000001</v>
+        <v>3.8074</v>
       </c>
       <c r="G6" t="n">
         <v>-2.938900000000002</v>
@@ -922,13 +922,13 @@
         <v>68.658</v>
       </c>
       <c r="S6" t="n">
-        <v>-8.620800000000001</v>
+        <v>-2.9658</v>
       </c>
       <c r="T6" t="n">
-        <v>-7.0342</v>
+        <v>-4.750299999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.5866</v>
+        <v>1.7851</v>
       </c>
       <c r="V6" t="n">
         <v>-16.6502</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>7.167</v>
+        <v>7.121099999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>18.9884</v>
+        <v>8.007899999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-11.8214</v>
+        <v>-0.8869999999999996</v>
       </c>
       <c r="G7" t="n">
-        <v>26.8799</v>
+        <v>0.09419999999999984</v>
       </c>
       <c r="H7" t="n">
-        <v>11.6013</v>
+        <v>-0.004399999999999959</v>
       </c>
       <c r="I7" t="n">
-        <v>15.2787</v>
+        <v>0.09850000000000003</v>
       </c>
       <c r="J7" t="n">
-        <v>43.1277</v>
+        <v>12.5525</v>
       </c>
       <c r="K7" t="n">
-        <v>24.9071</v>
+        <v>7.2893</v>
       </c>
       <c r="L7" t="n">
-        <v>18.2208</v>
+        <v>5.2629</v>
       </c>
       <c r="M7" t="n">
-        <v>-16.2474</v>
+        <v>-12.4585</v>
       </c>
       <c r="N7" t="n">
-        <v>-13.3056</v>
+        <v>-7.293900000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.9417</v>
+        <v>-5.164499999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-14.381</v>
+        <v>9.2783</v>
       </c>
       <c r="Q7" t="n">
-        <v>-48.4784</v>
+        <v>-12.9896</v>
       </c>
       <c r="R7" t="n">
-        <v>34.0975</v>
+        <v>22.2678</v>
       </c>
       <c r="S7" t="n">
-        <v>1.433</v>
+        <v>2.5738</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5969</v>
+        <v>0.6247</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1641</v>
+        <v>1.9491</v>
       </c>
       <c r="V7" t="n">
-        <v>-6.7653</v>
+        <v>-4.8249</v>
       </c>
       <c r="W7" t="n">
-        <v>21.7413</v>
+        <v>7.8201</v>
       </c>
       <c r="X7" t="n">
-        <v>-28.5066</v>
+        <v>-12.645</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>6.7749</v>
+        <v>4.270600000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>9.447100000000001</v>
+        <v>14.136</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.672</v>
+        <v>-9.865499999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09419999999999984</v>
+        <v>26.8799</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.004399999999999959</v>
+        <v>11.6013</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09850000000000003</v>
+        <v>15.2787</v>
       </c>
       <c r="J8" t="n">
-        <v>12.5525</v>
+        <v>43.1277</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2893</v>
+        <v>24.9071</v>
       </c>
       <c r="L8" t="n">
-        <v>5.2629</v>
+        <v>18.2208</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.4585</v>
+        <v>-16.2474</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.293900000000001</v>
+        <v>-13.3056</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.164499999999999</v>
+        <v>-2.9417</v>
       </c>
       <c r="P8" t="n">
-        <v>9.2783</v>
+        <v>-14.381</v>
       </c>
       <c r="Q8" t="n">
-        <v>-12.9896</v>
+        <v>-48.4784</v>
       </c>
       <c r="R8" t="n">
-        <v>22.2678</v>
+        <v>34.0975</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2277</v>
+        <v>-1.4633</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0637</v>
+        <v>-2.2548</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1639999999999999</v>
+        <v>0.7914999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.8249</v>
+        <v>-6.7653</v>
       </c>
       <c r="W8" t="n">
-        <v>7.8201</v>
+        <v>21.7413</v>
       </c>
       <c r="X8" t="n">
-        <v>-12.645</v>
+        <v>-28.5066</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4692999999999998</v>
+        <v>1.7426</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3069999999999997</v>
+        <v>1.4864</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7763000000000001</v>
+        <v>0.2561</v>
       </c>
       <c r="G9" t="n">
         <v>3.2078</v>
@@ -1156,13 +1156,13 @@
         <v>3.2475</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.5328</v>
+        <v>-1.3211</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.5233</v>
+        <v>-1.3438</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0095</v>
+        <v>0.02279999999999996</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. SEGEV</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8014</v>
+        <v>-0.4407000000000005</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0683</v>
+        <v>0.4430999999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2668</v>
+        <v>-0.884</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4873</v>
+        <v>1.2932</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2737</v>
+        <v>-2.9931</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7863</v>
+        <v>4.2863</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7695</v>
+        <v>3.1139</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7695</v>
+        <v>-1.0882</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.2023</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2822</v>
+        <v>-1.821</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5041</v>
+        <v>-1.9049</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7863</v>
+        <v>0.08430000000000037</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-5.1031</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>5.5669</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5461</v>
+        <v>1.8384</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>-1.0682</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2473</v>
+        <v>2.9066</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-4.0363</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-7.5365</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>I. SEGEV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.180699999999999</v>
+        <v>-0.5434</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3144</v>
+        <v>-1.0683</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1337999999999999</v>
+        <v>0.5249</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2932</v>
+        <v>-0.4873</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9931</v>
+        <v>-1.2737</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2863</v>
+        <v>0.7863</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1139</v>
+        <v>-0.7695</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0882</v>
+        <v>-0.7695</v>
       </c>
       <c r="L11" t="n">
-        <v>4.2023</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.821</v>
+        <v>0.2822</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9049</v>
+        <v>-0.5041</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08430000000000037</v>
+        <v>0.7863</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.1031</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5.5669</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0987</v>
+        <v>-0.288</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.8256</v>
+        <v>-0.2987</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9243</v>
+        <v>0.0108</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.0363</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.5002</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.5365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.736</v>
+        <v>-2.23</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3198999999999999</v>
+        <v>-1.0276</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4161</v>
+        <v>-1.2024</v>
       </c>
       <c r="G12" t="n">
         <v>1.7902</v>
@@ -1390,13 +1390,13 @@
         <v>1.6239</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1497000000000001</v>
+        <v>-0.6438000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8417000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9915</v>
+        <v>-0.7778</v>
       </c>
       <c r="V12" t="n">
         <v>-2.6805</v>
@@ -1423,13 +1423,13 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.286700000000001</v>
+        <v>-2.3407</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4798999999999998</v>
+        <v>1.0578</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.766799999999999</v>
+        <v>-3.3984</v>
       </c>
       <c r="G13" t="n">
         <v>4.389699999999999</v>
@@ -1468,13 +1468,13 @@
         <v>4.1754</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1921</v>
+        <v>-0.2458</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8389</v>
+        <v>-1.2612</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3532</v>
+        <v>1.0152</v>
       </c>
       <c r="V13" t="n">
         <v>-3.4691</v>
@@ -1501,13 +1501,13 @@
         <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.7217</v>
+        <v>-5.398700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.1342</v>
+        <v>-8.6243</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4125</v>
+        <v>3.2256</v>
       </c>
       <c r="G14" t="n">
         <v>-6.6107</v>
@@ -1546,13 +1546,13 @@
         <v>9.7423</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9663999999999998</v>
+        <v>1.2893</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9679</v>
+        <v>-0.4585</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9346</v>
+        <v>1.7474</v>
       </c>
       <c r="V14" t="n">
         <v>-2.3969</v>
@@ -1579,13 +1579,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.6859</v>
+        <v>-7.2918</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.5721</v>
+        <v>-5.4226</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.1137</v>
+        <v>-1.869</v>
       </c>
       <c r="G15" t="n">
         <v>-4.5936</v>
@@ -1624,13 +1624,13 @@
         <v>4.8711</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6795</v>
+        <v>0.7143999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6712</v>
+        <v>-0.522</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.008200000000000013</v>
+        <v>1.2365</v>
       </c>
       <c r="V15" t="n">
         <v>-4.5724</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.479</v>
+        <v>-7.639600000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.196</v>
+        <v>-10.3407</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.283</v>
+        <v>2.701099999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.9617</v>
+        <v>-26.4819</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.960199999999999</v>
+        <v>-2.762399999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-10.0015</v>
+        <v>-23.7197</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.2423</v>
+        <v>7.475299999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3594</v>
+        <v>18.5614</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.8828</v>
+        <v>-11.0863</v>
       </c>
       <c r="M16" t="n">
-        <v>-8.7194</v>
+        <v>-33.9569</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.6008</v>
+        <v>-21.3241</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.1187</v>
+        <v>-12.6333</v>
       </c>
       <c r="P16" t="n">
-        <v>5.335</v>
+        <v>50.5658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.0309</v>
+        <v>-14.6135</v>
       </c>
       <c r="R16" t="n">
-        <v>11.3659</v>
+        <v>65.1789</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.3496</v>
+        <v>-4.7628</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.2458</v>
+        <v>-7.5228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1041</v>
+        <v>2.7597</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4976</v>
+        <v>-26.9605</v>
       </c>
       <c r="W16" t="n">
-        <v>6.3225</v>
+        <v>4.3199</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.8249</v>
+        <v>-31.2804</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>-17.1178</v>
+        <v>-7.667899999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.6284</v>
+        <v>-6.270899999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.4893</v>
+        <v>-1.3971</v>
       </c>
       <c r="G17" t="n">
-        <v>-26.4819</v>
+        <v>-14.9617</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.762399999999999</v>
+        <v>-4.960199999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-23.7197</v>
+        <v>-10.0015</v>
       </c>
       <c r="J17" t="n">
-        <v>7.475299999999999</v>
+        <v>-6.2423</v>
       </c>
       <c r="K17" t="n">
-        <v>18.5614</v>
+        <v>-1.3594</v>
       </c>
       <c r="L17" t="n">
-        <v>-11.0863</v>
+        <v>-4.8828</v>
       </c>
       <c r="M17" t="n">
-        <v>-33.9569</v>
+        <v>-8.7194</v>
       </c>
       <c r="N17" t="n">
-        <v>-21.3241</v>
+        <v>-3.6008</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.6333</v>
+        <v>-5.1187</v>
       </c>
       <c r="P17" t="n">
-        <v>50.5658</v>
+        <v>5.335</v>
       </c>
       <c r="Q17" t="n">
-        <v>-14.6135</v>
+        <v>-6.0309</v>
       </c>
       <c r="R17" t="n">
-        <v>65.1789</v>
+        <v>11.3659</v>
       </c>
       <c r="S17" t="n">
-        <v>-14.2411</v>
+        <v>0.4614</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.8108</v>
+        <v>-0.3205</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.4301</v>
+        <v>0.7817000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-26.9605</v>
+        <v>1.4976</v>
       </c>
       <c r="W17" t="n">
-        <v>4.3199</v>
+        <v>6.3225</v>
       </c>
       <c r="X17" t="n">
-        <v>-31.2804</v>
+        <v>-4.8249</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>-47.5404</v>
+        <v>-27.7253</v>
       </c>
       <c r="E18" t="n">
-        <v>-55.6511</v>
+        <v>-38.8119</v>
       </c>
       <c r="F18" t="n">
-        <v>8.1104</v>
+        <v>11.0863</v>
       </c>
       <c r="G18" t="n">
         <v>16.3235</v>
@@ -1858,13 +1858,13 @@
         <v>65.8747</v>
       </c>
       <c r="S18" t="n">
-        <v>-32.3687</v>
+        <v>-12.5535</v>
       </c>
       <c r="T18" t="n">
-        <v>-27.9756</v>
+        <v>-11.1365</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.3933</v>
+        <v>-1.4173</v>
       </c>
       <c r="V18" t="n">
         <v>20.23</v>
@@ -1891,13 +1891,13 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>110.9617</v>
+        <v>155.0324</v>
       </c>
       <c r="E19" t="n">
-        <v>101.5342</v>
+        <v>115.7237</v>
       </c>
       <c r="F19" t="n">
-        <v>9.426700000000006</v>
+        <v>39.3073</v>
       </c>
       <c r="G19" t="n">
         <v>183.8293</v>
@@ -1933,16 +1933,16 @@
         <v>-534.653</v>
       </c>
       <c r="R19" t="n">
-        <v>536.9741</v>
+        <v>536.9740999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-61.9892</v>
+        <v>-17.9184</v>
       </c>
       <c r="T19" t="n">
-        <v>-60.397</v>
+        <v>-46.2071</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.593</v>
+        <v>28.2872</v>
       </c>
       <c r="V19" t="n">
         <v>-13.1985</v>
